--- a/StructureDefinition-ViewJoinMap.xlsx
+++ b/StructureDefinition-ViewJoinMap.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-20T08:14:58+00:00</t>
+    <t>2026-06-09T19:54:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
